--- a/Result/profitability/3416.xlsx
+++ b/Result/profitability/3416.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.75</v>
       </c>
       <c r="M2" t="n">
-        <v>1.82625</v>
+        <v>1.885</v>
       </c>
       <c r="N2" t="n">
-        <v>38.3725</v>
+        <v>38.45875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.96</v>
       </c>
       <c r="M3" t="n">
-        <v>1.82</v>
+        <v>1.92625</v>
       </c>
       <c r="N3" t="n">
-        <v>37.5625</v>
+        <v>37.75</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.93</v>
       </c>
       <c r="M4" t="n">
-        <v>1.8575</v>
+        <v>1.935</v>
       </c>
       <c r="N4" t="n">
-        <v>37.105</v>
+        <v>36.90375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>1.69</v>
       </c>
       <c r="M5" t="n">
-        <v>1.83625</v>
+        <v>1.9975</v>
       </c>
       <c r="N5" t="n">
-        <v>36.80625</v>
+        <v>36.705</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.2</v>
       </c>
       <c r="M6" t="n">
-        <v>1.8375</v>
+        <v>1.865</v>
       </c>
       <c r="N6" t="n">
-        <v>36.51875</v>
+        <v>36.70125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.84</v>
       </c>
       <c r="M7" t="n">
-        <v>1.66</v>
+        <v>1.70625</v>
       </c>
       <c r="N7" t="n">
-        <v>36.53125</v>
+        <v>36.74</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.05</v>
       </c>
       <c r="M8" t="n">
-        <v>1.5275</v>
+        <v>1.6125</v>
       </c>
       <c r="N8" t="n">
-        <v>36.64125</v>
+        <v>37.09875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>1.18</v>
       </c>
       <c r="N13" t="n">
-        <v>38.17875</v>
+        <v>38.17874999999999</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3416</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1177</v>
+      </c>
+      <c r="D75" t="n">
+        <v>704</v>
+      </c>
+      <c r="E75" t="n">
+        <v>473</v>
+      </c>
+      <c r="F75" t="n">
+        <v>40.18</v>
+      </c>
+      <c r="G75" t="n">
+        <v>231</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>19.63%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>21</v>
+      </c>
+      <c r="J75" t="n">
+        <v>252</v>
+      </c>
+      <c r="K75" t="n">
+        <v>200</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.9175</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.36</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3777777777777778</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.659999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1002190580503832</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.084033613445378</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.8100000000000023</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01976091729690177</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
